--- a/problems/marketing/1.youth_policy/eval/answer_key/2_추천리스트_정답.xlsx
+++ b/problems/marketing/1.youth_policy/eval/answer_key/2_추천리스트_정답.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="타게팅" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="타게팅" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -536,7 +536,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>회원 만 나이가 정책 연령(연령_min~연령_max, 양끝 포함) 안. 만 나이 = 기준일(2026-06-28) 기준이며, 생일이 아직 안 지났으면 한 살 뺀다(연도만 빼면 틀림)</t>
+          <t>회원 만 나이가 정책 연령(연령_최소~연령_최대, 양끝 포함) 안. 만 나이 = 기준일(2026-06-28) 기준이며, 생일이 아직 안 지났으면 한 살 뺀다(연도만 빼면 틀림)</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>소득상한_월_원이 있으면 회원 월소득_원이 그 이하(같으면 통과) / 빈칸=모두</t>
+          <t>월소득상한(원)이 있으면 회원 월소득(원)이 그 이하(같으면 통과) / 빈칸=모두</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>연소득상한_원이 있으면 회원 연소득_원이 그 이하(같으면 통과). 월소득과 별개 / 빈칸=모두</t>
+          <t>연소득상한(원)이 있으면 회원 연소득(원)이 그 이하(같으면 통과). 월소득과 별개 / 빈칸=모두</t>
         </is>
       </c>
     </row>
